--- a/data/decks.xlsx
+++ b/data/decks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikas\Desktop\vikash\Games\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47FAF0B-BFDF-4FE7-B58B-6B779BC33C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2827B646-FF93-42F2-86FF-9986947D76FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,6 @@
     <sheet name="hard" sheetId="4" r:id="rId4"/>
     <sheet name="extreme" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">fun!$C$52:$C$101</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3191" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3241" uniqueCount="1044">
   <si>
     <t>id</t>
   </si>
@@ -2820,186 +2817,12 @@
     <t>Sample extreme card 50 for the female performer. Replace this workbook row with final content later if needed.</t>
   </si>
   <si>
-    <t>1. Video call pe camera on karke ghutno pe baith jao, scarf se blindfold kar lo aur sirf nose se apni pussy lips ko 2 minute tak dheere rub karo, har 15 second mein bolo “Main tumhari personal toy hoon my king”.</t>
-  </si>
-  <si>
-    <t>2. All fours pe crawl karke camera ke saamne aao, apni soles ko tongue se tickling lick karo aur hasne wali awaaz mein bolo “Yeh tumhari submissive ki favorite jagah hai”.</t>
-  </si>
-  <si>
-    <t>3. Haath peeche light scarf se tie karne do, phir camera mein pussy ko spread karke gentle blow kisses do aur har kiss ke baad “Thank you for letting your submissive serve on call” whisper karo.</t>
-  </si>
-  <si>
-    <t>4. Poori nangi ho jao, doggy style pose mein gaand flash karke hips hilao aur beg karo “Please inspect your submissive girlfriend on video my dominant love”.</t>
-  </si>
-  <si>
-    <t>5. Blindfold laga ke camera ke saamne baith jao, apni fingers ko ek ek karke lollipop jaise chuso aur har finger ke baad “Yeh sirf aapke liye hai my king” bolo.</t>
-  </si>
-  <si>
-    <t>6. Camera pe let jao, sirf tongue tip se apni nipples ko bina haath lagaye 3 minute tak tease karo aur submissive eyes se camera dekho.</t>
-  </si>
-  <si>
-    <t>7. Camera ke saamne khadi ho ke pussy lips gently spread karke dikhao aur pyar se bolo “Yeh sirf aapka submissive part hai my king”.</t>
-  </si>
-  <si>
-    <t>8. Ankles light scarf se bind karne do, floor pe let jao aur apne boobs ko camera mein dikhaate hue heels ke saath massage style mein rub karo.</t>
-  </si>
-  <si>
-    <t>9. Camera on karke pee karo, phir ghutno pe baith ke apni inner thighs ko loving kisses se clean karo aur har kiss pe “I love cleaning for my king” bolo.</t>
-  </si>
-  <si>
-    <t>10. Blindfolded rehke camera ke saamne ass cheeks spread karke tongue se dheere lick karo aur whisper karo “Aap mere king ho, main aapki hoon”.</t>
-  </si>
-  <si>
-    <t>11. Crawl karke camera ke paas aao, sirf teeth se apni thighs pe very gentle love bites banao aur har bite ke baad kiss kar do.</t>
-  </si>
-  <si>
-    <t>12. Nangi ho ke wall ke against khadi ho jao, legs spread karke camera mein invite karo “Check your submissive girlfriend completely exposed on video”.</t>
-  </si>
-  <si>
-    <t>13. Blindfold karke camera ke saamne pussy ke upar hot breath blow karo phir soft kisses do aur bolo “Main pleasure dene ke liye hi video pe hoon”.</t>
-  </si>
-  <si>
-    <t>14. All fours pe baith ke camera ke saamne lower back pe tongue se small heart shape lick karke banao.</t>
-  </si>
-  <si>
-    <t>15. Camera ke saamne baith ke apni saliva collect karo, tongue pe dikhao aur pyar se swallow karo bolte hue “Aapka har cheez special hai my king”.</t>
-  </si>
-  <si>
-    <t>16. Wrists light scarf se bandhwa ke sirf lips aur chin se apni pussy ko tap-tap massage karo camera pe.</t>
-  </si>
-  <si>
-    <t>17. Nangi spread legs pose mein baith jao camera ke saamne, pussy lightly flash karke bolo “Yeh sab aapke control mein hai on video”.</t>
-  </si>
-  <si>
-    <t>18. Blindfolded rehke camera pe face daal ke apni thighs ke beech sirf cheeks se soft rub karo aur bolo “I love being trapped for you”.</t>
-  </si>
-  <si>
-    <t>19. Camera ke saamne let jao, har toe nail pe tongue se romantic circle banao aur “You own every inch of your submissive on call” whisper karo.</t>
-  </si>
-  <si>
-    <t>20. Haath tied hone do, doggy position mein camera mein aao aur sirf muh se apni pussy ko long romantic kiss do.</t>
-  </si>
-  <si>
-    <t>21. Nangi khadi ho ke wet pussy ko fingers se thapki do aur describe karo “Yeh sirf aapke pleasure ke liye ready hai my king”.</t>
-  </si>
-  <si>
-    <t>22. Blindfold laga ke camera pe apni pussy lips ko dono taraf se lips se sandwich kiss karo.</t>
-  </si>
-  <si>
-    <t>23. Camera ke saamne baith ke tongue bahar nikaal ke apni pussy ke saamne hold karke rakh do aur beg karo “Please tell your submissive what to do next”.</t>
-  </si>
-  <si>
-    <t>24. Thighs light scarf se bind karne do, camera pe face daal ke deep sniff karo aur bolo “Your voice makes me so submissive on call”.</t>
-  </si>
-  <si>
-    <t>25. Camera on karke pee karo phir tongue se drops catch karo jaise treasure ho.</t>
-  </si>
-  <si>
-    <t>26. Blindfold karke camera pe ass cheeks ko kiss karte hue har kiss pe “Thank you for owning me on video” bolo.</t>
-  </si>
-  <si>
-    <t>27. All fours pe baith ke camera ke saamne hips ko nose se nuzzle style mein rub karo pyar se.</t>
-  </si>
-  <si>
-    <t>28. Haath tied hone do, sirf teeth se apni top ke buttons ek ek kholo camera pe.</t>
-  </si>
-  <si>
-    <t>29. Nangi spread legs mein baith ke apni asshole lightly flash karke bolo “Yeh bhi aapka hai my king on video”.</t>
-  </si>
-  <si>
-    <t>30. Blindfolded rehke camera pe pussy pe upper lip se upar-neeche slide karo jaise soft stroking.</t>
-  </si>
-  <si>
-    <t>31. Camera ke saamne let jao, har toe pe tongue se small heart banao.</t>
-  </si>
-  <si>
-    <t>32. Light bondage mein pussy ke upar tongue ko slowly wave karo bina touch kiye camera pe.</t>
-  </si>
-  <si>
-    <t>33. Apni saliva palm pe collect karke usse pussy rub karo aur camera mein dikhao.</t>
-  </si>
-  <si>
-    <t>34. Crawl karke camera ke neeche aao aur apne feet ko worship kisses do.</t>
-  </si>
-  <si>
-    <t>35. Blindfold laga ke inner thighs pe tongue se “Property of my King” likho camera pe.</t>
-  </si>
-  <si>
-    <t>36. Camera ke saamne khadi ho ke apni nipples khud pinch karte hue moan karo.</t>
-  </si>
-  <si>
-    <t>37. Haath peeche tied karke tongue tip se apni asshole ke around tease circles banao.</t>
-  </si>
-  <si>
-    <t>38. Nangi let jao camera pe aur invite karo “Use your submissive girlfriend’s face as your throne on video”.</t>
-  </si>
-  <si>
-    <t>39. Blindfolded rehke pussy lips ko lips se sandwich style kiss karo camera pe.</t>
-  </si>
-  <si>
-    <t>40. All fours pe baith ke hips hilate hue beg karo “Please command your submissive on call my king”.</t>
-  </si>
-  <si>
-    <t>41. Tongue bahar nikaal ke camera mein pussy ke saamne hold karke rakh do.</t>
-  </si>
-  <si>
-    <t>42. Ankles bondage mein camera pe face daal ke deep sniff karo.</t>
-  </si>
-  <si>
-    <t>43. Camera on karke pee karo phir pussy ko ek ek kiss se thank you bolo.</t>
-  </si>
-  <si>
-    <t>44. Blindfold karke ass cheeks ke beech nose daal ke 30 seconds dheere breathe karo camera pe.</t>
-  </si>
-  <si>
-    <t>45. Haath tied hone do, muh se pussy aur clit ko cover karke suck karo camera pe.</t>
-  </si>
-  <si>
-    <t>46. Nangi khadi ho ke pussy spread karke flash karo aur bolo “Your submissive is dripping for you on video”.</t>
-  </si>
-  <si>
-    <t>47. Blindfolded rehke apne toes ko one by one candy jaise chuso camera pe.</t>
-  </si>
-  <si>
-    <t>48. Wrists tied hone do, sirf tongue se inner thighs ko long slow licks do camera pe.</t>
-  </si>
-  <si>
-    <t>49. Nangi doggy position mein baith ke gaand spread karke beg karo “Please look at your submissive’s ass my king on video”.</t>
-  </si>
-  <si>
-    <t>50. Camera ke saamne ghutno pe baith ke tongue bahar nikaal ke pussy ke niche se clit tak ek long lick karo aur bolo “I live to serve you on video call my dominant boyfriend”.</t>
-  </si>
-  <si>
     <t>fun-female-1</t>
   </si>
   <si>
     <t>Fun Queen Sample 1</t>
   </si>
   <si>
-    <t>2. All fours pe crawl karke camera ke saamne aao, apni soles ko tongue se tickling lick karo jab tak tum has na jao.</t>
-  </si>
-  <si>
-    <t>3. Haath peeche light scarf se tie karne do, camera mein pussy spread karke gentle blow kisses do aur har kiss ke baad “Thank you for letting your submissive serve on call” bolo.</t>
-  </si>
-  <si>
-    <t>6. Camera pe let jao, sirf tongue tip se apni nipples ko bina haath lagaye 3 minute tak tease karo submissive eyes se camera dekhte hue.</t>
-  </si>
-  <si>
-    <t>8. Ankles light scarf se bind karne do, floor pe let jao aur boobs ko camera mein dikhaate hue heels ke saath massage style rub karo.</t>
-  </si>
-  <si>
-    <t>9. Camera on karke pee karo, phir ghutno pe baith ke inner thighs ko loving kisses se clean karo aur har kiss pe “I love cleaning for my king” bolo.</t>
-  </si>
-  <si>
-    <t>11. Crawl karke camera ke paas aao, sirf teeth se thighs pe very gentle love bites banao aur har bite ke baad kiss kar do.</t>
-  </si>
-  <si>
-    <t>18. Blindfolded rehke camera pe face daal ke thighs ke beech sirf cheeks se soft rub karo aur bolo “I love being trapped for you”.</t>
-  </si>
-  <si>
-    <t>22. Blindfold laga ke camera pe pussy lips ko dono taraf se lips se sandwich kiss karo.</t>
-  </si>
-  <si>
     <t>fun-female-2</t>
   </si>
   <si>
@@ -3046,6 +2869,306 @@
   </si>
   <si>
     <t>Fun Queen Sample 9</t>
+  </si>
+  <si>
+    <t>1. Dice roll kiya toh apna top slowly utaaro, camera ke saamne apne boobs ko haathon se dabao aur seductive smile ke saath bolo, “Baby, yeh sab sirf tumhare liye hai, main tumhari naughty girlfriend hoon.”</t>
+  </si>
+  <si>
+    <t>2. Skirt upar kar ke apni panty ko side mein kheecho, camera zoom karo aur boli, “Dekho na darling, kitni wet ho gayi hoon tumhare liye… romantic hai na?”</t>
+  </si>
+  <si>
+    <t>3. Apne nipples ko tease karte hue 10 second tak moan karo aur bolo, “Yeh humiliation hai baby, lekin main tumse pyar karti hoon isliye kar rahi hoon.”</t>
+  </si>
+  <si>
+    <t>4. Camera ke saamne doggy style pose mein baitho, ass upar kar ke thoda spank do aur seductive voice mein, “Spank me harder daddy, main tumhari personal slut hoon.”</t>
+  </si>
+  <si>
+    <t>5. Apna bra utaar ke camera pe phenko, phir haathon se boobs ko cup kar ke bolo, “Ab yeh dono tumhare hain, touch karne ka mann kar raha hai na?”</t>
+  </si>
+  <si>
+    <t>6. Slow striptease dance karo full song ka, end mein panty mein hi camera ko kiss kar ke bolo, “Yeh romantic humiliation sirf tumhare liye baby.”</t>
+  </si>
+  <si>
+    <t>7. Apni pussy ko finger se touch kar ke dikhao, phir chat ke bolo, “Meri taste tumhe pasand hai na? Main tumhari dirty little secret hoon.”</t>
+  </si>
+  <si>
+    <t>8. Mirror ke saamne khade ho ke apna reflection dekhte hue apne body ko oil lagaao aur camera ko bolo, “Dekho kitni sexy ban gayi hoon tumhare liye.”</t>
+  </si>
+  <si>
+    <t>9. Apne ass ko camera ke bilkul close laao, spread kar ke bolo, “Yeh hole bhi tumhara hai darling, kabhi kabhi humiliate karna mujhe.”</t>
+  </si>
+  <si>
+    <t>10. Kneel down pose mein baith ke haath peeche karke boobs forward karo aur bolo, “Main tumhari obedient girlfriend hoon, jo bhi bolo karti hoon.”</t>
+  </si>
+  <si>
+    <t>11. Apne panties utaar ke camera pe phenko, phir nangi baith ke legs spread kar ke 20 second tak finger tease karo.</t>
+  </si>
+  <si>
+    <t>12. Romantic song bajao aur uspe lap dance style mein dance karo jaise main tumhare saamne hoon, end mein “I love you but I’m your slut too.”</t>
+  </si>
+  <si>
+    <t>13. Apni tongue dikhao aur bolo, “Yeh tongue tumhari pussy ke liye ready hai baby, ab main khud ko touch kar rahi hoon tumhare liye.”</t>
+  </si>
+  <si>
+    <t>14. Boobs ko squeeze karte hue moan karo aur boli, “Dard ho raha hai lekin maza bhi aa raha hai… tumhari wajah se.”</t>
+  </si>
+  <si>
+    <t>15. Camera ke saamne 69 position pose mein let jaao aur pretend karo jaise main tumhe suck kar rahi hoon, dirty talk karte hue.</t>
+  </si>
+  <si>
+    <t>16. Apne nipples ko ice cube se rub karo (agar hai toh) aur shiver karte hue bolo, “Yeh cold touch tumhara hot touch yaad dila raha hai.”</t>
+  </si>
+  <si>
+    <t>17. Doggy style mein camera ke peeche muh ghuma ke bolo, “Fuck me with your eyes baby, main tumhari whore ban gayi hoon aaj.”</t>
+  </si>
+  <si>
+    <t>18. Apni clit ko circle mein rub karte hue eyes camera mein daal ke bolo, “Main almost cumming hoon… permission do na daddy?”</t>
+  </si>
+  <si>
+    <t>19. Bra aur panty dono utaar ke full nude ho jaao, phir hands up karke twirl karo aur bolo, “Puri tarah tumhari property hoon.”</t>
+  </si>
+  <si>
+    <t>20. Apne body pe “Yours Only” likho lipstick se aur camera pe dikhao, phir kiss kar ke bolo, “Romantic humiliation complete baby.”</t>
+  </si>
+  <si>
+    <t>21. Slow motion mein apni pussy ko finger fuck karo aur loud moan karo, “Yeh sound sirf tum sun sakte ho darling.”</t>
+  </si>
+  <si>
+    <t>22. Ass upar kar ke mirror mein dekh ke spank karo 10 baar aur har baar bolo, “Thank you baby for humiliating me.”</t>
+  </si>
+  <si>
+    <t>23. Nangi baith ke legs wide open kar ke camera ko blow kiss do aur boli, “Yeh meri wet pussy ka gift hai tumhare liye.”</t>
+  </si>
+  <si>
+    <t>24. Apne boobs ko lick karne ki koshish karo aur fail hone pe cute humiliation face banao, phir hans ke bolo, “Main tumhari clumsy sexy girl hoon.”</t>
+  </si>
+  <si>
+    <t>25. Phone ko bed pe rakh ke missionary pose mein let jaao aur pretend fuck karte hue moan karo, “Harder baby… main tumhari hoon.”</t>
+  </si>
+  <si>
+    <t>26. Apni panties ko muh mein daal ke 10 second tak rakho aur camera mein aankh maarto hue bolo, “Taste of my juices for you.”</t>
+  </si>
+  <si>
+    <t>27. Wall ke saamne khade ho ke ass out kar ke twerk karo aur bolo, “Yeh ass shake sirf tumhare entertainment ke liye hai.”</t>
+  </si>
+  <si>
+    <t>28. Fingers ko apni pussy mein daal ke nikaal ke camera pe chat karo aur bolo, “Meri sweetness tumhe chahiye na?”</t>
+  </si>
+  <si>
+    <t>29. Romantic “I love you” bolte hue apne nipples ko pinch karo aur pain wala moan do.</t>
+  </si>
+  <si>
+    <t>30. Full nude ho ke yoga pose (downward dog) mein jaao aur bolo, “Flexible hoon tumhare liye baby, use me.”</t>
+  </si>
+  <si>
+    <t>31. Camera ke saamne sit kar ke legs upar kar ke spread karo aur boli, “Yeh view sirf tum dekh sakte ho, mera secret.”</t>
+  </si>
+  <si>
+    <t>32. Apne body pe kiss marks banane ki acting karo aur bolo, “Jaise tum mujhe mark kar rahe ho… romantic hai na?”</t>
+  </si>
+  <si>
+    <t>33. Slow sensual dance karte hue apni pussy ko touch kar ke shiver karo aur bolo, “Tum door ho phir bhi main wet ho rahi hoon.”</t>
+  </si>
+  <si>
+    <t>34. Kneeling position mein haath jod ke beg karo, “Please daddy, mujhe aaj humiliate karo on camera.”</t>
+  </si>
+  <si>
+    <t>35. Apni ass cheeks ko spread kar ke hold karo 15 second aur bolo, “Yeh tight hole bhi tumhara hai.”</t>
+  </si>
+  <si>
+    <t>36. Boobs ko press kar ke cleavage dikhao aur dirty voice mein, “Fuck my tits baby, main ready hoon.”</t>
+  </si>
+  <si>
+    <t>37. Nangi let ke pillow ko hug kar ke grind karo jaise tum ho aur moan karo.</t>
+  </si>
+  <si>
+    <t>38. Camera pe apni fingers suck karte hue bolo, “Yeh fingers abhi meri pussy mein the… taste karo.”</t>
+  </si>
+  <si>
+    <t>39. Romantic poem type mein bolo “Tumse pyar karti hoon lekin aaj main tumhari randi banna chahti hoon” aur pose do.</t>
+  </si>
+  <si>
+    <t>40. Apni clit ko vibrator style se (finger se) tease kar ke edge karo aur beg, “Mujhe cum karne do na please.”</t>
+  </si>
+  <si>
+    <t>41. Side pose mein let ke one leg upar kar ke full view do aur bolo, “Yeh angle sabse sexy hai tumhare liye.”</t>
+  </si>
+  <si>
+    <t>42. Apne nipples ko twist karte hue face pe humiliation expression daal ke bolo, “Main tumhari toy hoon aaj.”</t>
+  </si>
+  <si>
+    <t>43. Camera ke saamne squat kar ke upar neeche ho aur boobs bounce karo, “Bounce for my man.”</t>
+  </si>
+  <si>
+    <t>44. Panty ko sirf ek taraf kheech ke finger karo aur loud orgasm face banao.</t>
+  </si>
+  <si>
+    <t>45. Nangi ho ke “Property of [tera naam]” likho body pe aur proudly dikhao.</t>
+  </si>
+  <si>
+    <t>46. Slow blowjob acting karo imaginary cock pe aur eyes camera mein, “Main tumhe pleasure de rahi hoon baby.”</t>
+  </si>
+  <si>
+    <t>47. Ass camera ke saamne laao aur spank karte hue count karo 1 to 10 with moans.</t>
+  </si>
+  <si>
+    <t>48. Legs up in air pose mein baith ke pussy show karo aur bolo, “Yeh tumhara personal playground hai.”</t>
+  </si>
+  <si>
+    <t>49. End mein full nude pose mein haath upar kar ke bolo, “Mission complete baby, ab tum mujhe reward doge na? I love you so much.”</t>
+  </si>
+  <si>
+    <t>50. Last dice task – sabse wild: Camera pe full nude dance karo, apne body ko touch karte hue final moan karo aur end mein kiss kar ke bolo, “Yeh poora game tumhara tha… main hamesha tumhari sexy humiliated girlfriend rahungi ❤️”</t>
+  </si>
+  <si>
+    <t>1. Ek ek kapda utarte hue camera ko dekho aur bol do – “Baby main tumhara personal stripper hoon aaj.”</t>
+  </si>
+  <si>
+    <t>2. Nanga hoke camera ke saamne ghutno pe baith jao aur haath jod ke beg karo – “Please mujhe apna slave bana lo.”</t>
+  </si>
+  <si>
+    <t>3. Apne nipples ko tease karte hue moan karo aur bol do – “Yeh sirf tumhare liye hai meri jaan.”</t>
+  </si>
+  <si>
+    <t>4. Doggy style mein camera ke saamne hips hilao aur piche se dekhte hue bol do – “Spank me baby, main tumhara naughty boy hoon.”</t>
+  </si>
+  <si>
+    <t>5. Apne body pe lipstick se likho “Property of [uski name]” aur camera ko dikhate hue kiss karo.</t>
+  </si>
+  <si>
+    <t>6. Slow lap dance style dance karo jaise koi imaginary lap pe baitha ho aur bol do – “Tumhare liye hi yeh body hai.”</t>
+  </si>
+  <si>
+    <t>7. Ek haath pehle se nanga hoke dusre haath se apne lund ko tease karo bina haath lagaye aur beg karo – “Please touch karne do.”</t>
+  </si>
+  <si>
+    <t>8. Camera ke saamne blowjob pose mein muh khol ke tongue bahar nikalo aur bol do – “Main tumhara personal toy hoon.”</t>
+  </si>
+  <si>
+    <t>9. Apni gaand ko camera ke saamne spread karke bol do – “Yeh hole sirf tumhara hai baby, use karo.”</t>
+  </si>
+  <si>
+    <t>10. Romantic voice mein gaana gao “Tum hi ho mera pyar” aur saath mein apne body ko sensual touch karte hue.</t>
+  </si>
+  <si>
+    <t>11. Nanga hoke mirror ke saamne khade ho jao aur camera ko dikhao – “Dekho kitna desperate hoon main tumhare liye.”</t>
+  </si>
+  <si>
+    <t>12. Apne balls ko gently squeeze karte hue moan karo aur bol do – “Yeh sab tumhara control mein hai.”</t>
+  </si>
+  <si>
+    <t>13. Camera pe kiss karte hue bol do – “Main tumhari randi hoon aaj raat.”</t>
+  </si>
+  <si>
+    <t>14. Slow motion mein apna lund stroke karo lekin edge mat karna aur bol do – “Sirf tumhare order pe hi cum karunga.”</t>
+  </si>
+  <si>
+    <t>15. Apne nipples ko ice cube se rub karo aur thandi si awaaz mein chillao – “Baby yeh punishment mujhe bahut pasand hai.”</t>
+  </si>
+  <si>
+    <t>16. Camera ke saamne crawl karo jaise kutta aur bol do – “Main tumhara obedient puppy hoon.”</t>
+  </si>
+  <si>
+    <t>17. Apni tongue se apni fingers chato aur bol do – “Jab tum yahan hoti toh yeh kaam main tumhare liye karta.”</t>
+  </si>
+  <si>
+    <t>18. Nanga hoke wall ke saamne haath upar karke khade raho 2 minute aur bol do – “Main tumhara prisoner hoon.”</t>
+  </si>
+  <si>
+    <t>19. Apne lund pe “I love you” likho aur camera ko close-up dikhate hue kiss karo.</t>
+  </si>
+  <si>
+    <t>20. Sexy voice mein bolte hue apni gaand ko pat pat karo – “Spank me harder baby, main deserve karta hoon.”</t>
+  </si>
+  <si>
+    <t>21. Camera ke saamne lotus position mein baitho aur apne lund ko tease karte hue romantic shayari sunao.</t>
+  </si>
+  <si>
+    <t>22. Apne lips pe lipstick lagao aur camera ko French kiss style mein chumo.</t>
+  </si>
+  <si>
+    <t>23. Nanga hoke bed pe let jao aur legs upar karke bol do – “Yeh pussy tumhari marzi hai aaj.”</t>
+  </si>
+  <si>
+    <t>24. Apne body pe oil lagao aur shiny body dikhate hue bol do – “Touch me baby, main tumhara slippery slave hoon.”</t>
+  </si>
+  <si>
+    <t>25. Camera ke saamne kneel karke haath peeche karke bol do – “Main tumhare control mein hoon, order do.”</t>
+  </si>
+  <si>
+    <t>26. Slow striptease karte hue apne underwear ko muh mein daal ke bol do – “Yeh tumhare liye gift hai.”</t>
+  </si>
+  <si>
+    <t>27. Apni gaand ko camera ke saamne mirror mein dikhate hue bol do – “Yeh ass sirf tumhare liye bana hai.”</t>
+  </si>
+  <si>
+    <t>28. Romantic humiliation style mein bol do – “Main tumhara personal whore hoon, use me as you like.”</t>
+  </si>
+  <si>
+    <t>29. Apne lund ko ribbon se baandh lo aur camera pe present karo – “Gift for my queen.”</t>
+  </si>
+  <si>
+    <t>30. Camera ke saamne dance karte hue apne hips ko circle mein ghumao aur moan karo.</t>
+  </si>
+  <si>
+    <t>31. Apni chest pe “Slave” likho aur camera ke saamne flex karte hue bol do – “Yeh body sirf tumhari property hai.”</t>
+  </si>
+  <si>
+    <t>32. Slow blowjob motion mein imaginary dick chuso aur bol do – “Main tumhara perfect cocksucker hoon.”</t>
+  </si>
+  <si>
+    <t>33. Nanga hoke camera ke saamne 10 baar “I am your bitch” bol do loud voice mein.</t>
+  </si>
+  <si>
+    <t>34. Apne nipples ko pinch karte hue bol do – “Pain bhi pleasure hai jab tum control karti ho.”</t>
+  </si>
+  <si>
+    <t>35. Camera pe apna lund close-up dikhate hue bol do – “Yeh sirf tumhare entertainment ke liye hai baby.”</t>
+  </si>
+  <si>
+    <t>36. Romantic voice mein gaana gao aur saath mein apne body ko caress karo jaise koi aur touch kar raha ho.</t>
+  </si>
+  <si>
+    <t>37. Doggy style mein camera ke saamne face down ass up pose karo aur bol do – “Fuck me with your eyes baby.”</t>
+  </si>
+  <si>
+    <t>38. Apne fingers ko muh mein daal ke chuso aur bol do – “Jab tum nahi hoti toh yeh kar leta hoon.”</t>
+  </si>
+  <si>
+    <t>39. Nanga hoke camera ke saamne salute karo aur bol do – “Ready for your commands my queen.”</t>
+  </si>
+  <si>
+    <t>40. Apni gaand ko gently spank karte hue bol do – “Yeh punishment mujhe bahut horny bana deta hai.”</t>
+  </si>
+  <si>
+    <t>41. Camera ke saamne lay jao aur legs wide spread karke bol do – “Open for you only.”</t>
+  </si>
+  <si>
+    <t>42. Sexy ASMR voice mein apne body parts ko naam lete hue describe karo – “Yeh mera lund sirf tumhara hai.”</t>
+  </si>
+  <si>
+    <t>43. Apne lund ko edge karte hue 1 minute tak ruk jao aur beg karo – “Please cum karne do baby.”</t>
+  </si>
+  <si>
+    <t>44. Camera ke saamne heart shape bana ke apne haathon se aur bol do – “My heart and body both yours.”</t>
+  </si>
+  <si>
+    <t>45. Nanga hoke twerk karo jaise ladkiyan karti hain aur bol do – “Main tumhari sissy slave hoon aaj.”</t>
+  </si>
+  <si>
+    <t>46. Apne lips ko bite karte hue camera ko seductive eyes se dekho aur bol do – “Come destroy me baby.”</t>
+  </si>
+  <si>
+    <t>47. Camera pe apna orgasm face dikhate hue pretend karo bina cum kiye aur bol do – “Yeh face sirf tumhare liye hai.”</t>
+  </si>
+  <si>
+    <t>48. Apne body pe kiss marks banane ke liye lipstick use karo aur bol do – “Tumhari kisses ka nishaan.”</t>
+  </si>
+  <si>
+    <t>49. Slow sensual massage khud ko dete hue bol do – “Yeh hands tumhare hote toh kitna maza aata.”</t>
+  </si>
+  <si>
+    <t>50. Last mein full nanga hoke camera ke saamne haath faila ke bol do – “Main completely yours hoon baby… ab dice roll karo aur next task do!” ❤️🔥</t>
   </si>
 </sst>
 </file>
@@ -3429,9 +3552,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3460,7 +3583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3489,7 +3612,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3518,7 +3641,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3547,7 +3670,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3576,7 +3699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3605,7 +3728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3634,7 +3757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3663,7 +3786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3692,7 +3815,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3721,7 +3844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3750,7 +3873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3779,7 +3902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3808,7 +3931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -3837,7 +3960,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3866,7 +3989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -3895,7 +4018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -3924,7 +4047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -3953,7 +4076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -3982,7 +4105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -4011,7 +4134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -4040,7 +4163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -4069,7 +4192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -4098,7 +4221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -4127,7 +4250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -4156,7 +4279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -4185,7 +4308,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -4214,7 +4337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -4243,7 +4366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -4272,7 +4395,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -4301,7 +4424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -4330,7 +4453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -4359,7 +4482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -4388,7 +4511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -4417,7 +4540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -4446,7 +4569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -4475,7 +4598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -4504,7 +4627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -4533,7 +4656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -4562,7 +4685,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -4591,7 +4714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -4620,7 +4743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -4649,7 +4772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -4678,7 +4801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -4707,7 +4830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -4736,7 +4859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -4765,7 +4888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -4794,7 +4917,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -4823,7 +4946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -4852,7 +4975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -4881,7 +5004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -4910,7 +5033,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -4936,7 +5059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -4962,7 +5085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -4988,7 +5111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -5014,7 +5137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -5040,7 +5163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -5066,7 +5189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -5092,7 +5215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -5118,7 +5241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -5144,7 +5267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -5170,7 +5293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -5196,7 +5319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -5222,7 +5345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -5248,7 +5371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -5274,7 +5397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -5300,7 +5423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -5326,7 +5449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -5352,7 +5475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>66</v>
       </c>
@@ -5378,7 +5501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -5404,7 +5527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -5430,7 +5553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -5456,7 +5579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>66</v>
       </c>
@@ -5482,7 +5605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -5508,7 +5631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -5534,7 +5657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>66</v>
       </c>
@@ -5560,7 +5683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>66</v>
       </c>
@@ -5586,7 +5709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -5612,7 +5735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -5638,7 +5761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -5664,7 +5787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -5690,7 +5813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -5716,7 +5839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -5742,7 +5865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -5768,7 +5891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -5794,7 +5917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -5820,7 +5943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -5846,7 +5969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -5872,7 +5995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -5898,7 +6021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -5924,7 +6047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -5950,7 +6073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -5976,7 +6099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -6002,7 +6125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -6028,7 +6151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -6054,7 +6177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -6080,7 +6203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -6106,7 +6229,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -6132,7 +6255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -6158,7 +6281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -6184,7 +6307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -6220,8 +6343,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I165"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.296875" bestFit="1" customWidth="1"/>
@@ -6234,7 +6357,7 @@
     <col min="9" max="9" width="5.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6263,7 +6386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -6271,7 +6394,7 @@
         <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>926</v>
+        <v>994</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -6292,7 +6415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -6300,7 +6423,7 @@
         <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>927</v>
+        <v>995</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -6321,7 +6444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -6329,7 +6452,7 @@
         <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>928</v>
+        <v>996</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -6350,7 +6473,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -6358,7 +6481,7 @@
         <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>929</v>
+        <v>997</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -6379,7 +6502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -6387,7 +6510,7 @@
         <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>930</v>
+        <v>998</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -6408,7 +6531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>132</v>
       </c>
@@ -6416,7 +6539,7 @@
         <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>931</v>
+        <v>999</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -6437,7 +6560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>134</v>
       </c>
@@ -6445,7 +6568,7 @@
         <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>932</v>
+        <v>1000</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -6466,7 +6589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -6474,7 +6597,7 @@
         <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>933</v>
+        <v>1001</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -6495,7 +6618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -6503,7 +6626,7 @@
         <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>934</v>
+        <v>1002</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -6524,7 +6647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>140</v>
       </c>
@@ -6532,7 +6655,7 @@
         <v>141</v>
       </c>
       <c r="C11" t="s">
-        <v>935</v>
+        <v>1003</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -6553,7 +6676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>142</v>
       </c>
@@ -6561,7 +6684,7 @@
         <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>936</v>
+        <v>1004</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -6582,7 +6705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>144</v>
       </c>
@@ -6590,7 +6713,7 @@
         <v>145</v>
       </c>
       <c r="C13" t="s">
-        <v>937</v>
+        <v>1005</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -6611,7 +6734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>146</v>
       </c>
@@ -6619,7 +6742,7 @@
         <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>938</v>
+        <v>1006</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -6640,7 +6763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>148</v>
       </c>
@@ -6648,7 +6771,7 @@
         <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>939</v>
+        <v>1007</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
@@ -6669,7 +6792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -6677,7 +6800,7 @@
         <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>940</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -6698,7 +6821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>152</v>
       </c>
@@ -6706,7 +6829,7 @@
         <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>941</v>
+        <v>1009</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -6727,7 +6850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>154</v>
       </c>
@@ -6735,7 +6858,7 @@
         <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>942</v>
+        <v>1010</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -6756,7 +6879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>156</v>
       </c>
@@ -6764,7 +6887,7 @@
         <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>943</v>
+        <v>1011</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
@@ -6785,7 +6908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>158</v>
       </c>
@@ -6793,7 +6916,7 @@
         <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>944</v>
+        <v>1012</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
@@ -6814,7 +6937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>160</v>
       </c>
@@ -6822,7 +6945,7 @@
         <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>945</v>
+        <v>1013</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
@@ -6843,7 +6966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>162</v>
       </c>
@@ -6851,7 +6974,7 @@
         <v>163</v>
       </c>
       <c r="C22" t="s">
-        <v>946</v>
+        <v>1014</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
@@ -6872,7 +6995,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>164</v>
       </c>
@@ -6880,7 +7003,7 @@
         <v>165</v>
       </c>
       <c r="C23" t="s">
-        <v>947</v>
+        <v>1015</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
@@ -6901,7 +7024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>166</v>
       </c>
@@ -6909,7 +7032,7 @@
         <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>948</v>
+        <v>1016</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
@@ -6930,7 +7053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>168</v>
       </c>
@@ -6938,7 +7061,7 @@
         <v>169</v>
       </c>
       <c r="C25" t="s">
-        <v>949</v>
+        <v>1017</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
@@ -6959,7 +7082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>170</v>
       </c>
@@ -6967,7 +7090,7 @@
         <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>950</v>
+        <v>1018</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -6988,7 +7111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>172</v>
       </c>
@@ -6996,7 +7119,7 @@
         <v>173</v>
       </c>
       <c r="C27" t="s">
-        <v>951</v>
+        <v>1019</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -7017,7 +7140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>174</v>
       </c>
@@ -7025,7 +7148,7 @@
         <v>175</v>
       </c>
       <c r="C28" t="s">
-        <v>952</v>
+        <v>1020</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
@@ -7046,7 +7169,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>176</v>
       </c>
@@ -7054,7 +7177,7 @@
         <v>177</v>
       </c>
       <c r="C29" t="s">
-        <v>953</v>
+        <v>1021</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -7075,7 +7198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>178</v>
       </c>
@@ -7083,7 +7206,7 @@
         <v>179</v>
       </c>
       <c r="C30" t="s">
-        <v>954</v>
+        <v>1022</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -7104,7 +7227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>180</v>
       </c>
@@ -7112,7 +7235,7 @@
         <v>181</v>
       </c>
       <c r="C31" t="s">
-        <v>955</v>
+        <v>1023</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
@@ -7133,7 +7256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>182</v>
       </c>
@@ -7141,7 +7264,7 @@
         <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>956</v>
+        <v>1024</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
@@ -7162,7 +7285,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>184</v>
       </c>
@@ -7170,7 +7293,7 @@
         <v>185</v>
       </c>
       <c r="C33" t="s">
-        <v>957</v>
+        <v>1025</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -7191,7 +7314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>186</v>
       </c>
@@ -7199,7 +7322,7 @@
         <v>187</v>
       </c>
       <c r="C34" t="s">
-        <v>958</v>
+        <v>1026</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
@@ -7220,7 +7343,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>188</v>
       </c>
@@ -7228,7 +7351,7 @@
         <v>189</v>
       </c>
       <c r="C35" t="s">
-        <v>959</v>
+        <v>1027</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
@@ -7249,7 +7372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>190</v>
       </c>
@@ -7257,7 +7380,7 @@
         <v>191</v>
       </c>
       <c r="C36" t="s">
-        <v>960</v>
+        <v>1028</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
@@ -7278,7 +7401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>192</v>
       </c>
@@ -7286,7 +7409,7 @@
         <v>193</v>
       </c>
       <c r="C37" t="s">
-        <v>961</v>
+        <v>1029</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
@@ -7307,7 +7430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>194</v>
       </c>
@@ -7315,7 +7438,7 @@
         <v>195</v>
       </c>
       <c r="C38" t="s">
-        <v>962</v>
+        <v>1030</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
@@ -7336,7 +7459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>196</v>
       </c>
@@ -7344,7 +7467,7 @@
         <v>197</v>
       </c>
       <c r="C39" t="s">
-        <v>963</v>
+        <v>1031</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
@@ -7365,7 +7488,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>198</v>
       </c>
@@ -7373,7 +7496,7 @@
         <v>199</v>
       </c>
       <c r="C40" t="s">
-        <v>964</v>
+        <v>1032</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
@@ -7394,7 +7517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>200</v>
       </c>
@@ -7402,7 +7525,7 @@
         <v>201</v>
       </c>
       <c r="C41" t="s">
-        <v>965</v>
+        <v>1033</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
@@ -7423,7 +7546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>202</v>
       </c>
@@ -7431,7 +7554,7 @@
         <v>203</v>
       </c>
       <c r="C42" t="s">
-        <v>966</v>
+        <v>1034</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
@@ -7452,7 +7575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>204</v>
       </c>
@@ -7460,7 +7583,7 @@
         <v>205</v>
       </c>
       <c r="C43" t="s">
-        <v>967</v>
+        <v>1035</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
@@ -7481,7 +7604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>206</v>
       </c>
@@ -7489,7 +7612,7 @@
         <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>968</v>
+        <v>1036</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
@@ -7510,7 +7633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>208</v>
       </c>
@@ -7518,7 +7641,7 @@
         <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>969</v>
+        <v>1037</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
@@ -7539,7 +7662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -7547,7 +7670,7 @@
         <v>211</v>
       </c>
       <c r="C46" t="s">
-        <v>970</v>
+        <v>1038</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
@@ -7568,7 +7691,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>212</v>
       </c>
@@ -7576,7 +7699,7 @@
         <v>213</v>
       </c>
       <c r="C47" t="s">
-        <v>971</v>
+        <v>1039</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
@@ -7597,7 +7720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -7605,7 +7728,7 @@
         <v>215</v>
       </c>
       <c r="C48" t="s">
-        <v>972</v>
+        <v>1040</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
@@ -7626,7 +7749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>216</v>
       </c>
@@ -7634,7 +7757,7 @@
         <v>217</v>
       </c>
       <c r="C49" t="s">
-        <v>973</v>
+        <v>1041</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -7663,7 +7786,7 @@
         <v>219</v>
       </c>
       <c r="C50" t="s">
-        <v>974</v>
+        <v>1042</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
@@ -7689,7 +7812,7 @@
         <v>221</v>
       </c>
       <c r="C51" t="s">
-        <v>975</v>
+        <v>1043</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
@@ -7709,13 +7832,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>976</v>
+        <v>926</v>
       </c>
       <c r="B52" t="s">
-        <v>977</v>
+        <v>927</v>
       </c>
       <c r="C52" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="D52" t="s">
         <v>69</v>
@@ -7735,13 +7858,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>986</v>
+        <v>928</v>
       </c>
       <c r="B53" t="s">
-        <v>994</v>
+        <v>936</v>
       </c>
       <c r="C53" t="s">
-        <v>978</v>
+        <v>945</v>
       </c>
       <c r="D53" t="s">
         <v>69</v>
@@ -7761,13 +7884,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>987</v>
+        <v>929</v>
       </c>
       <c r="B54" t="s">
-        <v>995</v>
+        <v>937</v>
       </c>
       <c r="C54" t="s">
-        <v>979</v>
+        <v>946</v>
       </c>
       <c r="D54" t="s">
         <v>69</v>
@@ -7787,13 +7910,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>988</v>
+        <v>930</v>
       </c>
       <c r="B55" t="s">
-        <v>996</v>
+        <v>938</v>
       </c>
       <c r="C55" t="s">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="D55" t="s">
         <v>69</v>
@@ -7813,13 +7936,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>989</v>
+        <v>931</v>
       </c>
       <c r="B56" t="s">
-        <v>997</v>
+        <v>939</v>
       </c>
       <c r="C56" t="s">
-        <v>930</v>
+        <v>948</v>
       </c>
       <c r="D56" t="s">
         <v>69</v>
@@ -7839,13 +7962,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>990</v>
+        <v>932</v>
       </c>
       <c r="B57" t="s">
-        <v>998</v>
+        <v>940</v>
       </c>
       <c r="C57" t="s">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="D57" t="s">
         <v>69</v>
@@ -7865,13 +7988,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>991</v>
+        <v>933</v>
       </c>
       <c r="B58" t="s">
-        <v>999</v>
+        <v>941</v>
       </c>
       <c r="C58" t="s">
-        <v>932</v>
+        <v>950</v>
       </c>
       <c r="D58" t="s">
         <v>69</v>
@@ -7891,13 +8014,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>992</v>
+        <v>934</v>
       </c>
       <c r="B59" t="s">
-        <v>1000</v>
+        <v>942</v>
       </c>
       <c r="C59" t="s">
-        <v>981</v>
+        <v>951</v>
       </c>
       <c r="D59" t="s">
         <v>69</v>
@@ -7917,13 +8040,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>993</v>
+        <v>935</v>
       </c>
       <c r="B60" t="s">
-        <v>1001</v>
+        <v>943</v>
       </c>
       <c r="C60" t="s">
-        <v>982</v>
+        <v>952</v>
       </c>
       <c r="D60" t="s">
         <v>69</v>
@@ -7949,7 +8072,7 @@
         <v>223</v>
       </c>
       <c r="C61" t="s">
-        <v>935</v>
+        <v>953</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
@@ -7975,7 +8098,7 @@
         <v>225</v>
       </c>
       <c r="C62" t="s">
-        <v>983</v>
+        <v>954</v>
       </c>
       <c r="D62" t="s">
         <v>69</v>
@@ -8001,7 +8124,7 @@
         <v>227</v>
       </c>
       <c r="C63" t="s">
-        <v>937</v>
+        <v>955</v>
       </c>
       <c r="D63" t="s">
         <v>69</v>
@@ -8027,7 +8150,7 @@
         <v>229</v>
       </c>
       <c r="C64" t="s">
-        <v>938</v>
+        <v>956</v>
       </c>
       <c r="D64" t="s">
         <v>69</v>
@@ -8053,7 +8176,7 @@
         <v>231</v>
       </c>
       <c r="C65" t="s">
-        <v>939</v>
+        <v>957</v>
       </c>
       <c r="D65" t="s">
         <v>69</v>
@@ -8079,7 +8202,7 @@
         <v>233</v>
       </c>
       <c r="C66" t="s">
-        <v>940</v>
+        <v>958</v>
       </c>
       <c r="D66" t="s">
         <v>69</v>
@@ -8105,7 +8228,7 @@
         <v>235</v>
       </c>
       <c r="C67" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="D67" t="s">
         <v>69</v>
@@ -8131,7 +8254,7 @@
         <v>237</v>
       </c>
       <c r="C68" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="D68" t="s">
         <v>69</v>
@@ -8157,7 +8280,7 @@
         <v>239</v>
       </c>
       <c r="C69" t="s">
-        <v>984</v>
+        <v>961</v>
       </c>
       <c r="D69" t="s">
         <v>69</v>
@@ -8183,7 +8306,7 @@
         <v>241</v>
       </c>
       <c r="C70" t="s">
-        <v>944</v>
+        <v>962</v>
       </c>
       <c r="D70" t="s">
         <v>69</v>
@@ -8209,7 +8332,7 @@
         <v>243</v>
       </c>
       <c r="C71" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="D71" t="s">
         <v>69</v>
@@ -8235,7 +8358,7 @@
         <v>245</v>
       </c>
       <c r="C72" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="D72" t="s">
         <v>69</v>
@@ -8261,7 +8384,7 @@
         <v>247</v>
       </c>
       <c r="C73" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="D73" t="s">
         <v>69</v>
@@ -8287,7 +8410,7 @@
         <v>249</v>
       </c>
       <c r="C74" t="s">
-        <v>948</v>
+        <v>966</v>
       </c>
       <c r="D74" t="s">
         <v>69</v>
@@ -8313,7 +8436,7 @@
         <v>251</v>
       </c>
       <c r="C75" t="s">
-        <v>949</v>
+        <v>967</v>
       </c>
       <c r="D75" t="s">
         <v>69</v>
@@ -8339,7 +8462,7 @@
         <v>253</v>
       </c>
       <c r="C76" t="s">
-        <v>950</v>
+        <v>968</v>
       </c>
       <c r="D76" t="s">
         <v>69</v>
@@ -8365,7 +8488,7 @@
         <v>255</v>
       </c>
       <c r="C77" t="s">
-        <v>951</v>
+        <v>969</v>
       </c>
       <c r="D77" t="s">
         <v>69</v>
@@ -8391,7 +8514,7 @@
         <v>257</v>
       </c>
       <c r="C78" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="D78" t="s">
         <v>69</v>
@@ -8417,7 +8540,7 @@
         <v>259</v>
       </c>
       <c r="C79" t="s">
-        <v>953</v>
+        <v>971</v>
       </c>
       <c r="D79" t="s">
         <v>69</v>
@@ -8443,7 +8566,7 @@
         <v>261</v>
       </c>
       <c r="C80" t="s">
-        <v>954</v>
+        <v>972</v>
       </c>
       <c r="D80" t="s">
         <v>69</v>
@@ -8469,7 +8592,7 @@
         <v>263</v>
       </c>
       <c r="C81" t="s">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="D81" t="s">
         <v>69</v>
@@ -8495,7 +8618,7 @@
         <v>265</v>
       </c>
       <c r="C82" t="s">
-        <v>956</v>
+        <v>974</v>
       </c>
       <c r="D82" t="s">
         <v>69</v>
@@ -8521,7 +8644,7 @@
         <v>267</v>
       </c>
       <c r="C83" t="s">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="D83" t="s">
         <v>69</v>
@@ -8547,7 +8670,7 @@
         <v>269</v>
       </c>
       <c r="C84" t="s">
-        <v>958</v>
+        <v>976</v>
       </c>
       <c r="D84" t="s">
         <v>69</v>
@@ -8573,7 +8696,7 @@
         <v>271</v>
       </c>
       <c r="C85" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="D85" t="s">
         <v>69</v>
@@ -8599,7 +8722,7 @@
         <v>273</v>
       </c>
       <c r="C86" t="s">
-        <v>960</v>
+        <v>978</v>
       </c>
       <c r="D86" t="s">
         <v>69</v>
@@ -8625,7 +8748,7 @@
         <v>275</v>
       </c>
       <c r="C87" t="s">
-        <v>961</v>
+        <v>979</v>
       </c>
       <c r="D87" t="s">
         <v>69</v>
@@ -8651,7 +8774,7 @@
         <v>277</v>
       </c>
       <c r="C88" t="s">
-        <v>962</v>
+        <v>980</v>
       </c>
       <c r="D88" t="s">
         <v>69</v>
@@ -8677,7 +8800,7 @@
         <v>279</v>
       </c>
       <c r="C89" t="s">
-        <v>963</v>
+        <v>981</v>
       </c>
       <c r="D89" t="s">
         <v>69</v>
@@ -8703,7 +8826,7 @@
         <v>281</v>
       </c>
       <c r="C90" t="s">
-        <v>964</v>
+        <v>982</v>
       </c>
       <c r="D90" t="s">
         <v>69</v>
@@ -8729,7 +8852,7 @@
         <v>283</v>
       </c>
       <c r="C91" t="s">
-        <v>965</v>
+        <v>983</v>
       </c>
       <c r="D91" t="s">
         <v>69</v>
@@ -8755,7 +8878,7 @@
         <v>285</v>
       </c>
       <c r="C92" t="s">
-        <v>966</v>
+        <v>984</v>
       </c>
       <c r="D92" t="s">
         <v>69</v>
@@ -8781,7 +8904,7 @@
         <v>287</v>
       </c>
       <c r="C93" t="s">
-        <v>967</v>
+        <v>985</v>
       </c>
       <c r="D93" t="s">
         <v>69</v>
@@ -8807,7 +8930,7 @@
         <v>289</v>
       </c>
       <c r="C94" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="D94" t="s">
         <v>69</v>
@@ -8833,7 +8956,7 @@
         <v>291</v>
       </c>
       <c r="C95" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="D95" t="s">
         <v>69</v>
@@ -8859,7 +8982,7 @@
         <v>293</v>
       </c>
       <c r="C96" t="s">
-        <v>970</v>
+        <v>988</v>
       </c>
       <c r="D96" t="s">
         <v>69</v>
@@ -8885,7 +9008,7 @@
         <v>295</v>
       </c>
       <c r="C97" t="s">
-        <v>971</v>
+        <v>989</v>
       </c>
       <c r="D97" t="s">
         <v>69</v>
@@ -8911,7 +9034,7 @@
         <v>297</v>
       </c>
       <c r="C98" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="D98" t="s">
         <v>69</v>
@@ -8937,7 +9060,7 @@
         <v>299</v>
       </c>
       <c r="C99" t="s">
-        <v>973</v>
+        <v>991</v>
       </c>
       <c r="D99" t="s">
         <v>69</v>
@@ -8963,7 +9086,7 @@
         <v>301</v>
       </c>
       <c r="C100" t="s">
-        <v>974</v>
+        <v>992</v>
       </c>
       <c r="D100" t="s">
         <v>69</v>
@@ -8989,7 +9112,7 @@
         <v>303</v>
       </c>
       <c r="C101" t="s">
-        <v>975</v>
+        <v>993</v>
       </c>
       <c r="D101" t="s">
         <v>69</v>
@@ -9005,6 +9128,256 @@
       </c>
       <c r="H101">
         <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C116" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C117" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C118" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C119" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C120" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C121" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C122" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C123" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C124" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C125" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C126" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C127" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C128" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C129" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C130" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C131" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C132" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C133" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C134" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C135" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C136" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C137" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C138" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C139" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C140" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C141" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C142" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C143" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C144" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C145" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C146" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C147" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C148" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C149" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C150" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C151" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C152" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C153" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C154" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C155" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C156" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C157" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C158" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C159" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C160" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C161" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C162" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C163" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C164" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C165" t="s">
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -9019,9 +9392,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9050,7 +9433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>304</v>
       </c>
@@ -9079,7 +9462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>308</v>
       </c>
@@ -9108,7 +9491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>311</v>
       </c>
@@ -9137,7 +9520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>315</v>
       </c>
@@ -9166,7 +9549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>318</v>
       </c>
@@ -9195,7 +9578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>322</v>
       </c>
@@ -9235,9 +9618,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9266,7 +9649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>325</v>
       </c>
@@ -9295,7 +9678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>328</v>
       </c>
@@ -9324,7 +9707,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>331</v>
       </c>
@@ -9353,7 +9736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>334</v>
       </c>
@@ -9382,7 +9765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>337</v>
       </c>
@@ -9411,7 +9794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>340</v>
       </c>
@@ -9440,7 +9823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>343</v>
       </c>
@@ -9469,7 +9852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>346</v>
       </c>
@@ -9498,7 +9881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>349</v>
       </c>
@@ -9527,7 +9910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>352</v>
       </c>
@@ -9556,7 +9939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>355</v>
       </c>
@@ -9585,7 +9968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>358</v>
       </c>
@@ -9614,7 +9997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>361</v>
       </c>
@@ -9643,7 +10026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>364</v>
       </c>
@@ -9672,7 +10055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>367</v>
       </c>
@@ -9701,7 +10084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>370</v>
       </c>
@@ -9730,7 +10113,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>373</v>
       </c>
@@ -9759,7 +10142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>376</v>
       </c>
@@ -9788,7 +10171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>379</v>
       </c>
@@ -9817,7 +10200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>382</v>
       </c>
@@ -9846,7 +10229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>385</v>
       </c>
@@ -9875,7 +10258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>388</v>
       </c>
@@ -9904,7 +10287,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>391</v>
       </c>
@@ -9933,7 +10316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>394</v>
       </c>
@@ -9962,7 +10345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>397</v>
       </c>
@@ -9991,7 +10374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>400</v>
       </c>
@@ -10020,7 +10403,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>403</v>
       </c>
@@ -10049,7 +10432,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>406</v>
       </c>
@@ -10078,7 +10461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>409</v>
       </c>
@@ -10107,7 +10490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>412</v>
       </c>
@@ -10136,7 +10519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>415</v>
       </c>
@@ -10165,7 +10548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>418</v>
       </c>
@@ -10194,7 +10577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>421</v>
       </c>
@@ -10223,7 +10606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>424</v>
       </c>
@@ -10252,7 +10635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>427</v>
       </c>
@@ -10281,7 +10664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>430</v>
       </c>
@@ -10310,7 +10693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>433</v>
       </c>
@@ -10339,7 +10722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>436</v>
       </c>
@@ -10368,7 +10751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>439</v>
       </c>
@@ -10397,7 +10780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>442</v>
       </c>
@@ -10426,7 +10809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>445</v>
       </c>
@@ -10455,7 +10838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>448</v>
       </c>
@@ -10484,7 +10867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>451</v>
       </c>
@@ -10513,7 +10896,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>454</v>
       </c>
@@ -10542,7 +10925,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>457</v>
       </c>
@@ -10571,7 +10954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>460</v>
       </c>
@@ -10600,7 +10983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>463</v>
       </c>
@@ -10629,7 +11012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>466</v>
       </c>
@@ -10658,7 +11041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>469</v>
       </c>
@@ -10687,7 +11070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>472</v>
       </c>
@@ -10716,7 +11099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>475</v>
       </c>
@@ -10745,7 +11128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>478</v>
       </c>
@@ -10774,7 +11157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>481</v>
       </c>
@@ -10803,7 +11186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>484</v>
       </c>
@@ -10832,7 +11215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>487</v>
       </c>
@@ -10861,7 +11244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>490</v>
       </c>
@@ -10890,7 +11273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>493</v>
       </c>
@@ -10919,7 +11302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>496</v>
       </c>
@@ -10948,7 +11331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>499</v>
       </c>
@@ -10977,7 +11360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>502</v>
       </c>
@@ -11006,7 +11389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>505</v>
       </c>
@@ -11035,7 +11418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>508</v>
       </c>
@@ -11064,7 +11447,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>511</v>
       </c>
@@ -11093,7 +11476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>514</v>
       </c>
@@ -11122,7 +11505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>517</v>
       </c>
@@ -11151,7 +11534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>520</v>
       </c>
@@ -11180,7 +11563,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>523</v>
       </c>
@@ -11209,7 +11592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>526</v>
       </c>
@@ -11238,7 +11621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>529</v>
       </c>
@@ -11267,7 +11650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>532</v>
       </c>
@@ -11296,7 +11679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>535</v>
       </c>
@@ -11325,7 +11708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>538</v>
       </c>
@@ -11354,7 +11737,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>541</v>
       </c>
@@ -11383,7 +11766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>544</v>
       </c>
@@ -11412,7 +11795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>547</v>
       </c>
@@ -11441,7 +11824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>550</v>
       </c>
@@ -11470,7 +11853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>553</v>
       </c>
@@ -11499,7 +11882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>556</v>
       </c>
@@ -11528,7 +11911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>559</v>
       </c>
@@ -11557,7 +11940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>562</v>
       </c>
@@ -11586,7 +11969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>565</v>
       </c>
@@ -11615,7 +11998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>568</v>
       </c>
@@ -11644,7 +12027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>571</v>
       </c>
@@ -11673,7 +12056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>574</v>
       </c>
@@ -11702,7 +12085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>577</v>
       </c>
@@ -11731,7 +12114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>580</v>
       </c>
@@ -11760,7 +12143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>583</v>
       </c>
@@ -11789,7 +12172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>586</v>
       </c>
@@ -11818,7 +12201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>589</v>
       </c>
@@ -11847,7 +12230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>592</v>
       </c>
@@ -11876,7 +12259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>595</v>
       </c>
@@ -11905,7 +12288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>598</v>
       </c>
@@ -11934,7 +12317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>601</v>
       </c>
@@ -11963,7 +12346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>604</v>
       </c>
@@ -11992,7 +12375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>607</v>
       </c>
@@ -12021,7 +12404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>610</v>
       </c>
@@ -12050,7 +12433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>613</v>
       </c>
@@ -12079,7 +12462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>616</v>
       </c>
@@ -12108,7 +12491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>619</v>
       </c>
@@ -12137,7 +12520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>622</v>
       </c>
@@ -12177,9 +12560,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12208,7 +12591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>625</v>
       </c>
@@ -12237,7 +12620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>629</v>
       </c>
@@ -12266,7 +12649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>632</v>
       </c>
@@ -12295,7 +12678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>635</v>
       </c>
@@ -12324,7 +12707,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>638</v>
       </c>
@@ -12353,7 +12736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>641</v>
       </c>
@@ -12382,7 +12765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>644</v>
       </c>
@@ -12411,7 +12794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>647</v>
       </c>
@@ -12440,7 +12823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>650</v>
       </c>
@@ -12469,7 +12852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>653</v>
       </c>
@@ -12498,7 +12881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>656</v>
       </c>
@@ -12527,7 +12910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>659</v>
       </c>
@@ -12556,7 +12939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>662</v>
       </c>
@@ -12585,7 +12968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>665</v>
       </c>
@@ -12614,7 +12997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>668</v>
       </c>
@@ -12643,7 +13026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>671</v>
       </c>
@@ -12672,7 +13055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>674</v>
       </c>
@@ -12701,7 +13084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>677</v>
       </c>
@@ -12730,7 +13113,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>680</v>
       </c>
@@ -12759,7 +13142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>683</v>
       </c>
@@ -12788,7 +13171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>686</v>
       </c>
@@ -12817,7 +13200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>689</v>
       </c>
@@ -12846,7 +13229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>692</v>
       </c>
@@ -12875,7 +13258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>695</v>
       </c>
@@ -12904,7 +13287,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>698</v>
       </c>
@@ -12933,7 +13316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>701</v>
       </c>
@@ -12962,7 +13345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>704</v>
       </c>
@@ -12991,7 +13374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>707</v>
       </c>
@@ -13020,7 +13403,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>710</v>
       </c>
@@ -13049,7 +13432,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>713</v>
       </c>
@@ -13078,7 +13461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>716</v>
       </c>
@@ -13107,7 +13490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>719</v>
       </c>
@@ -13136,7 +13519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>722</v>
       </c>
@@ -13165,7 +13548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>725</v>
       </c>
@@ -13194,7 +13577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>728</v>
       </c>
@@ -13223,7 +13606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>731</v>
       </c>
@@ -13252,7 +13635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>734</v>
       </c>
@@ -13281,7 +13664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>737</v>
       </c>
@@ -13310,7 +13693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>740</v>
       </c>
@@ -13339,7 +13722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>743</v>
       </c>
@@ -13368,7 +13751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>746</v>
       </c>
@@ -13397,7 +13780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>749</v>
       </c>
@@ -13426,7 +13809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>752</v>
       </c>
@@ -13455,7 +13838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>755</v>
       </c>
@@ -13484,7 +13867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>758</v>
       </c>
@@ -13513,7 +13896,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>761</v>
       </c>
@@ -13542,7 +13925,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>764</v>
       </c>
@@ -13571,7 +13954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>767</v>
       </c>
@@ -13600,7 +13983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>770</v>
       </c>
@@ -13629,7 +14012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>773</v>
       </c>
@@ -13658,7 +14041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>776</v>
       </c>
@@ -13687,7 +14070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>779</v>
       </c>
@@ -13716,7 +14099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>782</v>
       </c>
@@ -13745,7 +14128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>785</v>
       </c>
@@ -13774,7 +14157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>788</v>
       </c>
@@ -13803,7 +14186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>791</v>
       </c>
@@ -13832,7 +14215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>794</v>
       </c>
@@ -13861,7 +14244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>797</v>
       </c>
@@ -13890,7 +14273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>800</v>
       </c>
@@ -13919,7 +14302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>803</v>
       </c>
@@ -13948,7 +14331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>806</v>
       </c>
@@ -13977,7 +14360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>809</v>
       </c>
@@ -14006,7 +14389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>812</v>
       </c>
@@ -14035,7 +14418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>815</v>
       </c>
@@ -14064,7 +14447,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>818</v>
       </c>
@@ -14093,7 +14476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>821</v>
       </c>
@@ -14122,7 +14505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>824</v>
       </c>
@@ -14151,7 +14534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>827</v>
       </c>
@@ -14180,7 +14563,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>830</v>
       </c>
@@ -14209,7 +14592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>833</v>
       </c>
@@ -14238,7 +14621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>836</v>
       </c>
@@ -14267,7 +14650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>839</v>
       </c>
@@ -14296,7 +14679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>842</v>
       </c>
@@ -14325,7 +14708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>845</v>
       </c>
@@ -14354,7 +14737,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>848</v>
       </c>
@@ -14383,7 +14766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>851</v>
       </c>
@@ -14412,7 +14795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>854</v>
       </c>
@@ -14441,7 +14824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>857</v>
       </c>
@@ -14470,7 +14853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>860</v>
       </c>
@@ -14499,7 +14882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>863</v>
       </c>
@@ -14528,7 +14911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>866</v>
       </c>
@@ -14557,7 +14940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>869</v>
       </c>
@@ -14586,7 +14969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>872</v>
       </c>
@@ -14615,7 +14998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>875</v>
       </c>
@@ -14644,7 +15027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>878</v>
       </c>
@@ -14673,7 +15056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>881</v>
       </c>
@@ -14702,7 +15085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>884</v>
       </c>
@@ -14731,7 +15114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>887</v>
       </c>
@@ -14760,7 +15143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>890</v>
       </c>
@@ -14789,7 +15172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>893</v>
       </c>
@@ -14818,7 +15201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>896</v>
       </c>
@@ -14847,7 +15230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>899</v>
       </c>
@@ -14876,7 +15259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>902</v>
       </c>
@@ -14905,7 +15288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>905</v>
       </c>
@@ -14934,7 +15317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>908</v>
       </c>
@@ -14963,7 +15346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>911</v>
       </c>
@@ -14992,7 +15375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>914</v>
       </c>
@@ -15021,7 +15404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>917</v>
       </c>
@@ -15050,7 +15433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>920</v>
       </c>
@@ -15079,7 +15462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>923</v>
       </c>
